--- a/ops/finanzas/ARGENTINA CMC 2026 · 1 de 3 — Costos y pagos.xlsx
+++ b/ops/finanzas/ARGENTINA CMC 2026 · 1 de 3 — Costos y pagos.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2734,609 +2734,165 @@
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>Unifilas</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>Estimado del sheet, sin cotización</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>Vallado (500 vallas)</t>
+        </is>
+      </c>
+      <c r="B49" s="43" t="inlineStr">
+        <is>
+          <t>Bonificado por técnica</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E49" s="43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F49" s="38" t="n"/>
-      <c r="G49" s="34" t="n"/>
-      <c r="H49" s="37">
+      <c r="F49" s="45" t="n"/>
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="47">
         <f>IF(F49="","",F49*(1+N(G49)))</f>
         <v/>
       </c>
-      <c r="I49" s="36" t="n">
+      <c r="I49" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="37">
+      <c r="J49" s="47">
         <f>IF(OR(D49="Bonificado",D49="Reemplazado"),0,N(I49)*IF(H49="",N(K49),IF(E49="USD",H49,H49/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K49" s="38" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L49" s="37">
+      <c r="K49" s="45" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L49" s="47">
         <f>IF(D49="Alternativa","",J49-N(K49))</f>
         <v/>
       </c>
-      <c r="M49" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
+      <c r="M49" s="49" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="42" t="inlineStr">
-        <is>
-          <t>Vallado (500 vallas)</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="inlineStr">
-        <is>
-          <t>Bonificado por técnica</t>
-        </is>
-      </c>
-      <c r="C50" s="44" t="inlineStr">
-        <is>
-          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
-        </is>
-      </c>
-      <c r="D50" s="42" t="inlineStr">
-        <is>
-          <t>Bonificado</t>
-        </is>
-      </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Intercoms</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Proveedor a confirmar</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Ya comprados y pagados al 100%. El master los tenía en 2 cuotas al 24/08 y 23/09, sin abonar.</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F50" s="45" t="n"/>
-      <c r="G50" s="46" t="n"/>
-      <c r="H50" s="47">
+      <c r="F50" s="12" t="n">
+        <v>560</v>
+      </c>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="14">
         <f>IF(F50="","",F50*(1+N(G50)))</f>
         <v/>
       </c>
-      <c r="I50" s="48" t="n">
+      <c r="I50" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="47">
+      <c r="J50" s="14">
         <f>IF(OR(D50="Bonificado",D50="Reemplazado"),0,N(I50)*IF(H50="",N(K50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K50" s="45" t="n">
-        <v>1250</v>
-      </c>
-      <c r="L50" s="47">
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="14">
         <f>IF(D50="Alternativa","",J50-N(K50))</f>
         <v/>
       </c>
-      <c r="M50" s="49" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>Estimado del sheet</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F51" s="38" t="n"/>
-      <c r="G51" s="34" t="n"/>
-      <c r="H51" s="37">
-        <f>IF(F51="","",F51*(1+N(G51)))</f>
-        <v/>
-      </c>
-      <c r="I51" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="37">
-        <f>IF(OR(D51="Bonificado",D51="Reemplazado"),0,N(I51)*IF(H51="",N(K51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K51" s="38" t="n">
-        <v>500</v>
-      </c>
-      <c r="L51" s="37">
-        <f>IF(D51="Alternativa","",J51-N(K51))</f>
-        <v/>
-      </c>
-      <c r="M51" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
-        <is>
-          <t>Escoltas (2)</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>Estimado del sheet</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F52" s="38" t="n"/>
-      <c r="G52" s="34" t="n"/>
-      <c r="H52" s="37">
-        <f>IF(F52="","",F52*(1+N(G52)))</f>
-        <v/>
-      </c>
-      <c r="I52" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="37">
-        <f>IF(OR(D52="Bonificado",D52="Reemplazado"),0,N(I52)*IF(H52="",N(K52),IF(E52="USD",H52,H52/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K52" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L52" s="37">
-        <f>IF(D52="Alternativa","",J52-N(K52))</f>
-        <v/>
-      </c>
-      <c r="M52" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
-        <is>
-          <t>Master Mind Hit</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>Sala adicional</t>
-        </is>
-      </c>
-      <c r="D53" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F53" s="38" t="n"/>
-      <c r="G53" s="34" t="n"/>
-      <c r="H53" s="37">
-        <f>IF(F53="","",F53*(1+N(G53)))</f>
-        <v/>
-      </c>
-      <c r="I53" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="37">
-        <f>IF(OR(D53="Bonificado",D53="Reemplazado"),0,N(I53)*IF(H53="",N(K53),IF(E53="USD",H53,H53/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K53" s="38" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L53" s="37">
-        <f>IF(D53="Alternativa","",J53-N(K53))</f>
-        <v/>
-      </c>
-      <c r="M53" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
-        <is>
-          <t>Personal logístico</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>La hoja del master lo tiene en US$0</t>
-        </is>
-      </c>
-      <c r="D54" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E54" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F54" s="38" t="n"/>
-      <c r="G54" s="34" t="n"/>
-      <c r="H54" s="37">
-        <f>IF(F54="","",F54*(1+N(G54)))</f>
-        <v/>
-      </c>
-      <c r="I54" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="37">
-        <f>IF(OR(D54="Bonificado",D54="Reemplazado"),0,N(I54)*IF(H54="",N(K54),IF(E54="USD",H54,H54/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K54" s="38" t="n"/>
-      <c r="L54" s="37">
-        <f>IF(D54="Alternativa","",J54-N(K54))</f>
-        <v/>
-      </c>
-      <c r="M54" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master · valor en cero</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Intercoms</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Proveedor a confirmar</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Ya comprados y pagados al 100%. El master los tenía en 2 cuotas al 24/08 y 23/09, sin abonar.</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>560</v>
-      </c>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="14">
-        <f>IF(F55="","",F55*(1+N(G55)))</f>
-        <v/>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="14">
-        <f>IF(OR(D55="Bonificado",D55="Reemplazado"),0,N(I55)*IF(H55="",N(K55),IF(E55="USD",H55,H55/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="14">
-        <f>IF(D55="Alternativa","",J55-N(K55))</f>
-        <v/>
-      </c>
-      <c r="M55" s="16" t="inlineStr">
+      <c r="M50" s="16" t="inlineStr">
         <is>
           <t>Confirmado por Agustina el 03/09</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Subtotal Producción</t>
         </is>
       </c>
-      <c r="B56" s="18" t="n"/>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="18" t="n"/>
-      <c r="I56" s="18" t="n"/>
-      <c r="J56" s="19">
-        <f>SUMIF($D$49:$D$55,"&lt;&gt;Alternativa",$J$49:$J$55)</f>
-        <v/>
-      </c>
-      <c r="K56" s="19">
-        <f>SUM($K$49:$K$55)</f>
-        <v/>
-      </c>
-      <c r="L56" s="19">
-        <f>J56-K56</f>
-        <v/>
-      </c>
-      <c r="M56" s="18" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>EQUIPO</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t>Vuelos del equipo</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
-        </is>
-      </c>
-      <c r="D58" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E58" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="34" t="n"/>
-      <c r="H58" s="37">
-        <f>IF(F58="","",F58*(1+N(G58)))</f>
-        <v/>
-      </c>
-      <c r="I58" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="37">
-        <f>IF(OR(D58="Bonificado",D58="Reemplazado"),0,N(I58)*IF(H58="",N(K58),IF(E58="USD",H58,H58/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K58" s="38" t="n"/>
-      <c r="L58" s="37">
-        <f>IF(D58="Alternativa","",J58-N(K58))</f>
-        <v/>
-      </c>
-      <c r="M58" s="39" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
-        <is>
-          <t>Alojamiento del equipo</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
-        </is>
-      </c>
-      <c r="D59" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F59" s="38" t="n"/>
-      <c r="G59" s="34" t="n"/>
-      <c r="H59" s="37">
-        <f>IF(F59="","",F59*(1+N(G59)))</f>
-        <v/>
-      </c>
-      <c r="I59" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="37">
-        <f>IF(OR(D59="Bonificado",D59="Reemplazado"),0,N(I59)*IF(H59="",N(K59),IF(E59="USD",H59,H59/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K59" s="38" t="n"/>
-      <c r="L59" s="37">
-        <f>IF(D59="Alternativa","",J59-N(K59))</f>
-        <v/>
-      </c>
-      <c r="M59" s="39" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>Traslados internos y viáticos</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>Sin registro</t>
-        </is>
-      </c>
-      <c r="D60" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E60" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F60" s="38" t="n"/>
-      <c r="G60" s="34" t="n"/>
-      <c r="H60" s="37">
-        <f>IF(F60="","",F60*(1+N(G60)))</f>
-        <v/>
-      </c>
-      <c r="I60" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="37">
-        <f>IF(OR(D60="Bonificado",D60="Reemplazado"),0,N(I60)*IF(H60="",N(K60),IF(E60="USD",H60,H60/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K60" s="38" t="n"/>
-      <c r="L60" s="37">
-        <f>IF(D60="Alternativa","",J60-N(K60))</f>
-        <v/>
-      </c>
-      <c r="M60" s="39" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal Equipo</t>
-        </is>
-      </c>
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="18" t="n"/>
-      <c r="I61" s="18" t="n"/>
-      <c r="J61" s="19">
-        <f>SUMIF($D$58:$D$60,"&lt;&gt;Alternativa",$J$58:$J$60)</f>
-        <v/>
-      </c>
-      <c r="K61" s="19">
-        <f>SUM($K$58:$K$60)</f>
-        <v/>
-      </c>
-      <c r="L61" s="19">
-        <f>J61-K61</f>
-        <v/>
-      </c>
-      <c r="M61" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="52" t="inlineStr">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="19">
+        <f>SUMIF($D$49:$D$50,"&lt;&gt;Alternativa",$J$49:$J$50)</f>
+        <v/>
+      </c>
+      <c r="K51" s="19">
+        <f>SUM($K$49:$K$50)</f>
+        <v/>
+      </c>
+      <c r="L51" s="19">
+        <f>J51-K51</f>
+        <v/>
+      </c>
+      <c r="M51" s="18" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="52" t="inlineStr">
         <is>
           <t>COSTO TOTAL DEL EVENTO</t>
         </is>
       </c>
-      <c r="J63" s="53">
-        <f>J7+J10+J15+J21+J30+J43+J47+J56+J61</f>
-        <v/>
-      </c>
-      <c r="K63" s="53">
-        <f>K7+K10+K15+K21+K30+K43+K47+K56+K61</f>
-        <v/>
-      </c>
-      <c r="L63" s="53">
-        <f>L7+L10+L15+L21+L30+L43+L47+L56+L61</f>
+      <c r="J53" s="53">
+        <f>J7+J10+J15+J21+J30+J43+J47+J51</f>
+        <v/>
+      </c>
+      <c r="K53" s="53">
+        <f>K7+K10+K15+K21+K30+K43+K47+K51</f>
+        <v/>
+      </c>
+      <c r="L53" s="53">
+        <f>L7+L10+L15+L21+L30+L43+L47+L51</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M4"/>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A44:M44"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="A31:M31"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A57:M57"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A11:M11"/>
   </mergeCells>
@@ -3403,7 +2959,7 @@
         </is>
       </c>
       <c r="C7" s="56">
-        <f>'COSTOS UNIFICADOS'!J63</f>
+        <f>'COSTOS UNIFICADOS'!J53</f>
         <v/>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3419,7 +2975,7 @@
         </is>
       </c>
       <c r="C8" s="56">
-        <f>'COSTOS UNIFICADOS'!K63</f>
+        <f>'COSTOS UNIFICADOS'!K53</f>
         <v/>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3435,7 +2991,7 @@
         </is>
       </c>
       <c r="C9" s="57">
-        <f>'COSTOS UNIFICADOS'!L63</f>
+        <f>'COSTOS UNIFICADOS'!L53</f>
         <v/>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4198,7 +3754,7 @@
         </is>
       </c>
       <c r="D27" s="108">
-        <f>'COSTOS UNIFICADOS'!J63</f>
+        <f>'COSTOS UNIFICADOS'!J53</f>
         <v/>
       </c>
     </row>
@@ -4220,7 +3776,7 @@
         </is>
       </c>
       <c r="D29" s="110">
-        <f>'COSTOS UNIFICADOS'!J63-D13</f>
+        <f>'COSTOS UNIFICADOS'!J53-D13</f>
         <v/>
       </c>
     </row>
@@ -4242,7 +3798,7 @@
         </is>
       </c>
       <c r="D31" s="111">
-        <f>'COSTOS UNIFICADOS'!J63-D13-D23</f>
+        <f>'COSTOS UNIFICADOS'!J53-D13-D23</f>
         <v/>
       </c>
     </row>
